--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitionerrole.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole</t>
+    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -563,7 +563,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -582,7 +582,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>practitionerがどのような権限を持っているのかを知る必要がある - 何ができるのか？</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS|1.1.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -651,7 +651,7 @@
     <t>代理店に関連する特定の専門分野。 / Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -666,7 +666,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -688,7 +688,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1219,7 +1219,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="56.37890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.3671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1234,7 +1234,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.69921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.53125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.05859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitionerrole.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -563,7 +563,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -582,7 +582,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>practitionerがどのような権限を持っているのかを知る必要がある - 何ができるのか？</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PractitionerRole_VS</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -651,7 +651,7 @@
     <t>代理店に関連する特定の専門分野。 / Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -666,7 +666,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -688,7 +688,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
+    <t xml:space="preserve">Reference(HealthcareService)
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -1219,7 +1219,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.3671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1234,7 +1234,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.69921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.05859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.53125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
